--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119545342</v>
+        <v>119545349</v>
       </c>
       <c r="B55" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,25 +6148,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600895</v>
+        <v>600890</v>
       </c>
       <c r="R55" t="n">
-        <v>7064634</v>
+        <v>7064635</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6209,19 +6209,9 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6248,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119545349</v>
+        <v>119544891</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>91228</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6260,25 +6250,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6288,13 +6278,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600890</v>
+        <v>600974</v>
       </c>
       <c r="R56" t="n">
-        <v>7064635</v>
+        <v>7064652</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6350,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119542984</v>
+        <v>119543011</v>
       </c>
       <c r="B57" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,25 +6352,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6390,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>600727</v>
+        <v>600721</v>
       </c>
       <c r="R57" t="n">
-        <v>7064733</v>
+        <v>7064752</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6452,10 +6442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119545676</v>
+        <v>119543500</v>
       </c>
       <c r="B58" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6464,25 +6454,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6492,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>600752</v>
+        <v>600898</v>
       </c>
       <c r="R58" t="n">
-        <v>7064754</v>
+        <v>7064767</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6554,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119545637</v>
+        <v>119543431</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,21 +6560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600787</v>
+        <v>600805</v>
       </c>
       <c r="R59" t="n">
-        <v>7064724</v>
+        <v>7064825</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6656,10 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119543500</v>
+        <v>119543538</v>
       </c>
       <c r="B60" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6668,25 +6658,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6696,10 +6686,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600898</v>
+        <v>600891</v>
       </c>
       <c r="R60" t="n">
-        <v>7064767</v>
+        <v>7064754</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6758,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119544891</v>
+        <v>119545342</v>
       </c>
       <c r="B61" t="n">
-        <v>91228</v>
+        <v>91005</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,21 +6764,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6798,13 +6788,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600974</v>
+        <v>600895</v>
       </c>
       <c r="R61" t="n">
-        <v>7064652</v>
+        <v>7064634</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6831,9 +6821,19 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6860,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119545915</v>
+        <v>119545075</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6876,37 +6876,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Husmyran, Husmyran, Ång</t>
+          <t>Löningsberget, Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600718</v>
+        <v>600987</v>
       </c>
       <c r="R62" t="n">
-        <v>7064725</v>
+        <v>7064647</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119543205</v>
+        <v>119542980</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,25 +6974,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>600769</v>
+        <v>600739</v>
       </c>
       <c r="R63" t="n">
-        <v>7064768</v>
+        <v>7064717</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119545075</v>
+        <v>119543205</v>
       </c>
       <c r="B65" t="n">
-        <v>78262</v>
+        <v>91856</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7182,37 +7182,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Löningsberget, Löningsberget, Ång</t>
+          <t>Husmyran, Husmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>600987</v>
+        <v>600769</v>
       </c>
       <c r="R65" t="n">
-        <v>7064647</v>
+        <v>7064768</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7268,10 +7268,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119543431</v>
+        <v>119545915</v>
       </c>
       <c r="B66" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7284,21 +7284,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600805</v>
+        <v>600718</v>
       </c>
       <c r="R66" t="n">
-        <v>7064825</v>
+        <v>7064725</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7370,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119543538</v>
+        <v>119545676</v>
       </c>
       <c r="B67" t="n">
-        <v>90905</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7382,25 +7382,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600891</v>
+        <v>600752</v>
       </c>
       <c r="R67" t="n">
         <v>7064754</v>
@@ -7472,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119543011</v>
+        <v>119545637</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7484,25 +7484,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>600721</v>
+        <v>600787</v>
       </c>
       <c r="R68" t="n">
-        <v>7064752</v>
+        <v>7064724</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7574,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119542980</v>
+        <v>119542984</v>
       </c>
       <c r="B69" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7586,25 +7586,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600739</v>
+        <v>600727</v>
       </c>
       <c r="R69" t="n">
-        <v>7064717</v>
+        <v>7064733</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -6962,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119542980</v>
+        <v>119543099</v>
       </c>
       <c r="B63" t="n">
-        <v>91852</v>
+        <v>91821</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,25 +6974,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>6055</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>600739</v>
+        <v>600769</v>
       </c>
       <c r="R63" t="n">
-        <v>7064717</v>
+        <v>7064768</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119543099</v>
+        <v>119542980</v>
       </c>
       <c r="B64" t="n">
-        <v>91821</v>
+        <v>91852</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7076,25 +7076,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6055</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>600769</v>
+        <v>600739</v>
       </c>
       <c r="R64" t="n">
-        <v>7064768</v>
+        <v>7064717</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -6136,7 +6136,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119545349</v>
+        <v>119543500</v>
       </c>
       <c r="B55" t="n">
         <v>90562</v>
@@ -6172,14 +6172,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Löningsberget, Löningsberget, Ång</t>
+          <t>Husmyran, Husmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600890</v>
+        <v>600898</v>
       </c>
       <c r="R55" t="n">
-        <v>7064635</v>
+        <v>7064767</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6238,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119544891</v>
+        <v>119543538</v>
       </c>
       <c r="B56" t="n">
-        <v>91228</v>
+        <v>90905</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6254,37 +6254,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>898</v>
+        <v>2062</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Löningsberget, Löningsberget, Ång</t>
+          <t>Husmyran, Husmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600974</v>
+        <v>600891</v>
       </c>
       <c r="R56" t="n">
-        <v>7064652</v>
+        <v>7064754</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119543011</v>
+        <v>119545075</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6352,41 +6352,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Husmyran, Husmyran, Ång</t>
+          <t>Löningsberget, Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>600721</v>
+        <v>600987</v>
       </c>
       <c r="R57" t="n">
-        <v>7064752</v>
+        <v>7064647</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119543500</v>
+        <v>119542980</v>
       </c>
       <c r="B58" t="n">
-        <v>90562</v>
+        <v>91852</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6454,25 +6454,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>600898</v>
+        <v>600739</v>
       </c>
       <c r="R58" t="n">
-        <v>7064767</v>
+        <v>7064717</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119543431</v>
+        <v>119545342</v>
       </c>
       <c r="B59" t="n">
-        <v>89633</v>
+        <v>91005</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6556,38 +6556,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Husmyran, Husmyran, Ång</t>
+          <t>Löningsberget, Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600805</v>
+        <v>600895</v>
       </c>
       <c r="R59" t="n">
-        <v>7064825</v>
+        <v>7064634</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6617,9 +6617,19 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6646,10 +6656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119543538</v>
+        <v>119545637</v>
       </c>
       <c r="B60" t="n">
-        <v>90905</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6658,25 +6668,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2062</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6686,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600891</v>
+        <v>600787</v>
       </c>
       <c r="R60" t="n">
-        <v>7064754</v>
+        <v>7064724</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6748,10 +6758,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119545342</v>
+        <v>119544891</v>
       </c>
       <c r="B61" t="n">
-        <v>91005</v>
+        <v>91228</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,21 +6774,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6788,13 +6798,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600895</v>
+        <v>600974</v>
       </c>
       <c r="R61" t="n">
-        <v>7064634</v>
+        <v>7064652</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6821,19 +6831,9 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6860,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119545075</v>
+        <v>119545915</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6876,37 +6876,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Löningsberget, Löningsberget, Ång</t>
+          <t>Husmyran, Husmyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600987</v>
+        <v>600718</v>
       </c>
       <c r="R62" t="n">
-        <v>7064647</v>
+        <v>7064725</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119543099</v>
+        <v>119545676</v>
       </c>
       <c r="B63" t="n">
-        <v>91821</v>
+        <v>90527</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,25 +6974,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6055</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>600769</v>
+        <v>600752</v>
       </c>
       <c r="R63" t="n">
-        <v>7064768</v>
+        <v>7064754</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119542980</v>
+        <v>119543011</v>
       </c>
       <c r="B64" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>600739</v>
+        <v>600721</v>
       </c>
       <c r="R64" t="n">
-        <v>7064717</v>
+        <v>7064752</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119543205</v>
+        <v>119543431</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>89633</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7182,21 +7182,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>600769</v>
+        <v>600805</v>
       </c>
       <c r="R65" t="n">
-        <v>7064768</v>
+        <v>7064825</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7268,10 +7268,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119545915</v>
+        <v>119545349</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7284,34 +7284,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Husmyran, Husmyran, Ång</t>
+          <t>Löningsberget, Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600718</v>
+        <v>600890</v>
       </c>
       <c r="R66" t="n">
-        <v>7064725</v>
+        <v>7064635</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7370,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119545676</v>
+        <v>119543099</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>91821</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7382,25 +7382,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6055</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600752</v>
+        <v>600769</v>
       </c>
       <c r="R67" t="n">
-        <v>7064754</v>
+        <v>7064768</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119545637</v>
+        <v>119542984</v>
       </c>
       <c r="B68" t="n">
         <v>91884</v>
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>600787</v>
+        <v>600727</v>
       </c>
       <c r="R68" t="n">
-        <v>7064724</v>
+        <v>7064733</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7574,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119542984</v>
+        <v>119543205</v>
       </c>
       <c r="B69" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7590,21 +7590,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600727</v>
+        <v>600769</v>
       </c>
       <c r="R69" t="n">
-        <v>7064733</v>
+        <v>7064768</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7674,6 +7674,127 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122246433</v>
+      </c>
+      <c r="B70" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kläppsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>601460</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7064411</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Y-Sol-0437</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>längs ca 150 meter</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7750,7 +7750,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Y-Sol-0437</t>
+          <t>Y-Sol-0131</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7683,7 +7683,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,11 +7693,6 @@
       </c>
       <c r="E70" t="n">
         <v>1365</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,6 +7693,11 @@
       </c>
       <c r="E70" t="n">
         <v>1365</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7679,7 +7679,7 @@
         <v>122246433</v>
       </c>
       <c r="B70" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7795,6 +7795,327 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>124016571</v>
+      </c>
+      <c r="B71" t="n">
+        <v>96332</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NEFlärkåsvägen, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>601045</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7064584</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124016580</v>
+      </c>
+      <c r="B72" t="n">
+        <v>96332</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>53</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>NE Flärkåsvägen, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>601199</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7064447</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124016559</v>
+      </c>
+      <c r="B73" t="n">
+        <v>96205</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>NE Flärkåsvägen, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>600982</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7064644</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7797,7 +7797,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124016571</v>
+        <v>124016580</v>
       </c>
       <c r="B71" t="n">
         <v>96332</v>
@@ -7837,14 +7837,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NEFlärkåsvägen, Ång</t>
+          <t>NE Flärkåsvägen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601045</v>
+        <v>601199</v>
       </c>
       <c r="R71" t="n">
-        <v>7064584</v>
+        <v>7064447</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7904,7 +7904,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124016580</v>
+        <v>124016571</v>
       </c>
       <c r="B72" t="n">
         <v>96332</v>
@@ -7944,14 +7944,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NE Flärkåsvägen, Ång</t>
+          <t>NEFlärkåsvägen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>601199</v>
+        <v>601045</v>
       </c>
       <c r="R72" t="n">
-        <v>7064447</v>
+        <v>7064584</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8008,113 +8008,6 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>124016559</v>
-      </c>
-      <c r="B73" t="n">
-        <v>96205</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>2869</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Sphagnum wulfianum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>NE Flärkåsvägen, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>600982</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7064644</v>
-      </c>
-      <c r="S73" t="n">
-        <v>25</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Martin Bergström</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Martin Bergström</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7797,7 +7797,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124016580</v>
+        <v>124016571</v>
       </c>
       <c r="B71" t="n">
         <v>96332</v>
@@ -7837,14 +7837,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NE Flärkåsvägen, Ång</t>
+          <t>NEFlärkåsvägen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601199</v>
+        <v>601045</v>
       </c>
       <c r="R71" t="n">
-        <v>7064447</v>
+        <v>7064584</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7904,7 +7904,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124016571</v>
+        <v>124016580</v>
       </c>
       <c r="B72" t="n">
         <v>96332</v>
@@ -7944,14 +7944,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NEFlärkåsvägen, Ång</t>
+          <t>NE Flärkåsvägen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>601045</v>
+        <v>601199</v>
       </c>
       <c r="R72" t="n">
-        <v>7064584</v>
+        <v>7064447</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7837,7 +7837,7 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NEFlärkåsvägen, Ång</t>
+          <t>NE Flärkåsvägen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7797,7 +7797,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124016571</v>
+        <v>124016580</v>
       </c>
       <c r="B71" t="n">
         <v>96354</v>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601045</v>
+        <v>601199</v>
       </c>
       <c r="R71" t="n">
-        <v>7064584</v>
+        <v>7064447</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7904,7 +7904,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124016580</v>
+        <v>124016571</v>
       </c>
       <c r="B72" t="n">
         <v>96354</v>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>601199</v>
+        <v>601045</v>
       </c>
       <c r="R72" t="n">
-        <v>7064447</v>
+        <v>7064584</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>

--- a/artfynd/A 14807-2024 artfynd.xlsx
+++ b/artfynd/A 14807-2024 artfynd.xlsx
@@ -7797,7 +7797,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124016580</v>
+        <v>124016571</v>
       </c>
       <c r="B71" t="n">
         <v>96354</v>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601199</v>
+        <v>601045</v>
       </c>
       <c r="R71" t="n">
-        <v>7064447</v>
+        <v>7064584</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7904,7 +7904,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124016571</v>
+        <v>124016580</v>
       </c>
       <c r="B72" t="n">
         <v>96354</v>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>601045</v>
+        <v>601199</v>
       </c>
       <c r="R72" t="n">
-        <v>7064584</v>
+        <v>7064447</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
